--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99478</v>
+        <v>99488</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99488</v>
+        <v>99500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99500</v>
+        <v>99505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99505</v>
+        <v>99514</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1583,11 +1583,6 @@
       </c>
       <c r="E9" t="n">
         <v>345</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99514</v>
+        <v>99527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1583,6 +1583,11 @@
       </c>
       <c r="E9" t="n">
         <v>345</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sötgräs</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99527</v>
+        <v>99540</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99540</v>
+        <v>99543</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99543</v>
+        <v>99544</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -1569,7 +1569,7 @@
         <v>122285095</v>
       </c>
       <c r="B9" t="n">
-        <v>99544</v>
+        <v>99547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Y-Här-0095</t>
+          <t>Y-Här-0034</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,131 +1561,6 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Inventering av Mjällådalen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122285095</v>
-      </c>
-      <c r="B9" t="n">
-        <v>99547</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>345</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sötgräs</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cinna latifolia</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Trevir.) Griseb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Mjällådalen, V om Viksjö samhälle, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>623230</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6962625</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Härnösand</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Viksjö</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Y-Här-0034</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2012-09-18</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2012-09-18</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>en gammal åfåra, lövrik granskog, standskog, objekt med naturvärde</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Hans Sundström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 52716-2022 artfynd.xlsx
+++ b/artfynd/A 52716-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/143948</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/143949</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/420771</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/420772</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1871242</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1898012</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712487</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712488</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,6 +1951,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712489</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712490</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2113,8 +2178,28 @@
           <t>Inventering av Mjällådalen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2712491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>